--- a/output/upload/S00027_1950_튼튼이_치아보험_갱신형_무배당.xlsx
+++ b/output/upload/S00027_1950_튼튼이_치아보험_갱신형_무배당.xlsx
@@ -2611,17 +2611,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>1950013</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>6207005</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -2702,17 +2694,9 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>1950013</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>6207005</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">

--- a/output/upload/S00027_1950_튼튼이_치아보험_갱신형_무배당.xlsx
+++ b/output/upload/S00027_1950_튼튼이_치아보험_갱신형_무배당.xlsx
@@ -2611,11 +2611,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1950013</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 튼튼이 치아보험(갱신형) 무배당 5년만기(80세)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>195013</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 튼튼이 치아보험(갱신형) 무배당 5년만기(80세)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2694,11 +2714,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>1950013</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 튼튼이 치아보험(갱신형) 무배당 5년만기(80세)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>195013</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 튼튼이 치아보험(갱신형) 무배당 5년만기(80세)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00027_1950_튼튼이_치아보험_갱신형_무배당.xlsx
+++ b/output/upload/S00027_1950_튼튼이_치아보험_갱신형_무배당.xlsx
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>195013</t>
+          <t>1950013</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>195013</t>
+          <t>1950013</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">

--- a/output/upload/S00027_1950_튼튼이_치아보험_갱신형_무배당.xlsx
+++ b/output/upload/S00027_1950_튼튼이_치아보험_갱신형_무배당.xlsx
@@ -2817,20 +2817,72 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-      <c r="M9" s="6" t="n"/>
-      <c r="N9" s="6" t="n"/>
-      <c r="O9" s="6" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1950014</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 튼튼이 치아보험(갱신형) 무배당 10년만기(80세)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>1950014</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 튼튼이 치아보험(갱신형) 무배당 10년만기(80세)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P9" s="6" t="n"/>
       <c r="Q9" s="6" t="n"/>
       <c r="R9" s="6" t="n"/>
@@ -2868,20 +2920,72 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
-      <c r="M10" s="6" t="n"/>
-      <c r="N10" s="6" t="n"/>
-      <c r="O10" s="6" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>1950014</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 튼튼이 치아보험(갱신형) 무배당 10년만기(80세)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>1950014</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 튼튼이 치아보험(갱신형) 무배당 10년만기(80세)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P10" s="6" t="n"/>
       <c r="Q10" s="6" t="n"/>
       <c r="R10" s="6" t="n"/>

--- a/output/upload/S00027_1950_튼튼이_치아보험_갱신형_무배당.xlsx
+++ b/output/upload/S00027_1950_튼튼이_치아보험_갱신형_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -2716,22 +2716,22 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>1950013</t>
+          <t>1950014</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>한화생명 튼튼이 치아보험(갱신형) 무배당 5년만기(80세)</t>
+          <t>한화생명 튼튼이 치아보험(갱신형) 무배당 10년만기(80세)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>1950013</t>
+          <t>1950014</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>한화생명 튼튼이 치아보험(갱신형) 무배당 5년만기(80세)</t>
+          <t>한화생명 튼튼이 치아보험(갱신형) 무배당 10년만기(80세)</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2817,72 +2817,20 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>1950014</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 튼튼이 치아보험(갱신형) 무배당 10년만기(80세)</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>1950014</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 튼튼이 치아보험(갱신형) 무배당 10년만기(80세)</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="6" t="n"/>
       <c r="P9" s="6" t="n"/>
       <c r="Q9" s="6" t="n"/>
       <c r="R9" s="6" t="n"/>
@@ -2920,72 +2868,20 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>1950014</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 튼튼이 치아보험(갱신형) 무배당 10년만기(80세)</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>1950014</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 튼튼이 치아보험(갱신형) 무배당 10년만기(80세)</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
+      <c r="N10" s="6" t="n"/>
+      <c r="O10" s="6" t="n"/>
       <c r="P10" s="6" t="n"/>
       <c r="Q10" s="6" t="n"/>
       <c r="R10" s="6" t="n"/>
